--- a/PCA_Seul_decathlon_R.xlsx
+++ b/PCA_Seul_decathlon_R.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\θανάσης\Documents\Teaching\Perrotis_College\MSc\Academic Research\2025-2026\Session 9C - Principal Component Analysis\Good datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\θανάσης\Documents\Teaching\Perrotis_College\MSc\Academic Research\2025-2026\Session 8O - Principal Component Analysis\Good datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0673AA9E-1DDE-4448-BCB7-9B455B34E2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E49F459-7990-4E51-8AD7-3E1A0D5CE838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PCA_Seul_decathlon" sheetId="1" r:id="rId1"/>
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9.2157464767960745E-2</v>
+        <v>-9.2157464767960745E-2</v>
       </c>
       <c r="B2" s="1">
         <v>0.89603820177600602</v>
@@ -455,10 +455,10 @@
         <v>2.8291059456309231</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.39656154561448625</v>
+        <v>0.39656154561448625</v>
       </c>
       <c r="F2" s="1">
-        <v>3.6907024849726397E-2</v>
+        <v>-3.6907024849726397E-2</v>
       </c>
       <c r="G2" s="1">
         <v>1.6385648036482003</v>
@@ -470,12 +470,12 @@
         <v>0.38507740918830247</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.5372755071383265</v>
+        <v>0.5372755071383265</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>-1.2308141405676165</v>
+        <v>1.2308141405676165</v>
       </c>
       <c r="B3" s="1">
         <v>0.94953301979248539</v>
@@ -487,10 +487,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E3" s="1">
-        <v>-1.4088568223060798</v>
+        <v>1.4088568223060798</v>
       </c>
       <c r="F3" s="1">
-        <v>-1.0693324831458835</v>
+        <v>1.0693324831458835</v>
       </c>
       <c r="G3" s="1">
         <v>0.54540407797909563</v>
@@ -502,12 +502,12 @@
         <v>0.4534138035116354</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.23530489393089857</v>
+        <v>0.23530489393089857</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>-0.15154783095175134</v>
+        <v>0.15154783095175134</v>
       </c>
       <c r="B4" s="1">
         <v>0.92278561078424681</v>
@@ -519,10 +519,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.91546920845639601</v>
+        <v>0.91546920845639601</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.49144617299892362</v>
+        <v>0.49144617299892362</v>
       </c>
       <c r="G4" s="1">
         <v>0.38987308042454766</v>
@@ -534,12 +534,12 @@
         <v>0.82615777254799849</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.96389246682941088</v>
+        <v>0.96389246682941088</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>-2.101190196709442</v>
+        <v>2.101190196709442</v>
       </c>
       <c r="B5" s="1">
         <v>0.76230115673481114</v>
@@ -551,10 +551,10 @@
         <v>0.53204081962611061</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.26045461765594924</v>
+        <v>0.26045461765594924</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.64004550989385611</v>
+        <v>0.64004550989385611</v>
       </c>
       <c r="G5" s="1">
         <v>0.64316641929909635</v>
@@ -566,12 +566,12 @@
         <v>0.80752057409618183</v>
       </c>
       <c r="J5" s="1">
-        <v>0.6617036352282708</v>
+        <v>-0.6617036352282708</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>-0.70858850688252006</v>
+        <v>0.70858850688252006</v>
       </c>
       <c r="B6" s="1">
         <v>0.89603820177600602</v>
@@ -583,10 +583,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.6385372632361084</v>
+        <v>1.6385372632361084</v>
       </c>
       <c r="F6" s="1">
-        <v>-1.168398707742506</v>
+        <v>1.168398707742506</v>
       </c>
       <c r="G6" s="1">
         <v>-0.15670728241000306</v>
@@ -598,12 +598,12 @@
         <v>-0.21441914101184839</v>
       </c>
       <c r="J6" s="1">
-        <v>-1.4506067721465439</v>
+        <v>1.4506067721465439</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>-1.3700743095503056</v>
+        <v>1.3700743095503056</v>
       </c>
       <c r="B7" s="1">
         <v>1.6717130630149388</v>
@@ -615,10 +615,10 @@
         <v>1.3934402418779173</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.87293579346935057</v>
+        <v>0.87293579346935057</v>
       </c>
       <c r="F7" s="1">
-        <v>-1.5316415312634537</v>
+        <v>1.5316415312634537</v>
       </c>
       <c r="G7" s="1">
         <v>0.25656079680636551</v>
@@ -630,12 +630,12 @@
         <v>-1.0344558728918478</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.15740092737861275</v>
+        <v>0.15740092737861275</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>-0.15154783095175134</v>
+        <v>0.15154783095175134</v>
       </c>
       <c r="B8" s="1">
         <v>-0.12036334053707795</v>
@@ -647,10 +647,10 @@
         <v>0.81917396037671419</v>
       </c>
       <c r="E8" s="1">
-        <v>-2.2267493728514061E-2</v>
+        <v>2.2267493728514061E-2</v>
       </c>
       <c r="F8" s="1">
-        <v>-1.1849097451752761</v>
+        <v>1.1849097451752761</v>
       </c>
       <c r="G8" s="1">
         <v>-5.005745551545699E-2</v>
@@ -662,12 +662,12 @@
         <v>0.42856420557587838</v>
       </c>
       <c r="J8" s="1">
-        <v>1.1135466412315218</v>
+        <v>-1.1135466412315218</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>-0.60414338014549707</v>
+        <v>0.60414338014549707</v>
       </c>
       <c r="B9" s="1">
         <v>-0.38783743061946757</v>
@@ -679,10 +679,10 @@
         <v>0.24490767887551115</v>
       </c>
       <c r="E9" s="1">
-        <v>-0.98352267243566149</v>
+        <v>0.98352267243566149</v>
       </c>
       <c r="F9" s="1">
-        <v>-1.2344428574735888</v>
+        <v>1.2344428574735888</v>
       </c>
       <c r="G9" s="1">
         <v>-0.13004482568636694</v>
@@ -694,12 +694,12 @@
         <v>0.64599818751375671</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.76653575156362042</v>
+        <v>0.76653575156362042</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>-0.25599295768876817</v>
+        <v>0.25599295768876817</v>
       </c>
       <c r="B10" s="1">
         <v>6.6868522520596219E-2</v>
@@ -711,10 +711,10 @@
         <v>0.53204081962611061</v>
       </c>
       <c r="E10" s="1">
-        <v>-0.18389447067927711</v>
+        <v>0.18389447067927711</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.73911173449047862</v>
+        <v>0.73911173449047862</v>
       </c>
       <c r="G10" s="1">
         <v>0.10102979925181751</v>
@@ -726,12 +726,12 @@
         <v>1.1833707428745128</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.48756535705258158</v>
+        <v>0.48756535705258158</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>2.2527380276616198E-2</v>
+        <v>-2.2527380276616198E-2</v>
       </c>
       <c r="B11" s="1">
         <v>0.49482706665242154</v>
@@ -743,10 +743,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E11" s="1">
-        <v>-0.65176203553673484</v>
+        <v>0.65176203553673484</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.57400136016277625</v>
+        <v>0.57400136016277625</v>
       </c>
       <c r="G11" s="1">
         <v>1.3586090080500155</v>
@@ -758,12 +758,12 @@
         <v>9.9307032927090089E-2</v>
       </c>
       <c r="J11" s="1">
-        <v>1.1907086652452152</v>
+        <v>-1.1907086652452152</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>-0.9871088448479044</v>
+        <v>0.9871088448479044</v>
       </c>
       <c r="B12" s="1">
         <v>0.94953301979248539</v>
@@ -775,10 +775,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E12" s="1">
-        <v>0.48813348611598301</v>
+        <v>-0.48813348611598301</v>
       </c>
       <c r="F12" s="1">
-        <v>-1.4160642692340613</v>
+        <v>1.4160642692340613</v>
       </c>
       <c r="G12" s="1">
         <v>-1.006377043000202E-2</v>
@@ -790,12 +790,12 @@
         <v>1.2113265405522411</v>
       </c>
       <c r="J12" s="1">
-        <v>1.4615176918317279</v>
+        <v>-1.4615176918317279</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>-0.15154783095175134</v>
+        <v>0.15154783095175134</v>
       </c>
       <c r="B13" s="1">
         <v>0.65531152070185483</v>
@@ -807,10 +807,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.29448134964558198</v>
+        <v>0.29448134964558198</v>
       </c>
       <c r="F13" s="1">
-        <v>3.8849499841835801E-3</v>
+        <v>-3.8849499841835801E-3</v>
       </c>
       <c r="G13" s="1">
         <v>0.18990465499727283</v>
@@ -822,12 +822,12 @@
         <v>1.0870785508734537</v>
       </c>
       <c r="J13" s="1">
-        <v>-1.4431873467606102</v>
+        <v>1.4431873467606102</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>-0.70858850688252006</v>
+        <v>0.70858850688252006</v>
       </c>
       <c r="B14" s="1">
         <v>0.52157447566066006</v>
@@ -839,10 +839,10 @@
         <v>0.81917396037671419</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.9665093064408482</v>
+        <v>0.9665093064408482</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.27680268637291139</v>
+        <v>0.27680268637291139</v>
       </c>
       <c r="G14" s="1">
         <v>-0.52553793375364477</v>
@@ -854,12 +854,12 @@
         <v>-0.31692373249684885</v>
       </c>
       <c r="J14" s="1">
-        <v>-1.3608317249767652</v>
+        <v>1.3608317249767652</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>-0.81303363361953684</v>
+        <v>0.81303363361953684</v>
       </c>
       <c r="B15" s="1">
         <v>0.73555374772657267</v>
@@ -871,10 +871,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E15" s="1">
-        <v>-1.3067766263371816</v>
+        <v>1.3067766263371816</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.67306758475939887</v>
+        <v>0.67306758475939887</v>
       </c>
       <c r="G15" s="1">
         <v>0.43875425108454957</v>
@@ -886,12 +886,12 @@
         <v>1.1957955418423936</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.53579162206113728</v>
+        <v>0.53579162206113728</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>-0.67377346463684773</v>
+        <v>0.67377346463684773</v>
       </c>
       <c r="B16" s="1">
         <v>0.94953301979248539</v>
@@ -903,10 +903,10 @@
         <v>-4.2225461875090402E-2</v>
       </c>
       <c r="E16" s="1">
-        <v>-0.36253481362485351</v>
+        <v>0.36253481362485351</v>
       </c>
       <c r="F16" s="1">
-        <v>0.54874918526560357</v>
+        <v>-0.54874918526560357</v>
       </c>
       <c r="G16" s="1">
         <v>-5.4501198302730473E-2</v>
@@ -918,12 +918,12 @@
         <v>0.80130817461224146</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.64634106031152327</v>
+        <v>0.64634106031152327</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>-0.46488321116280795</v>
+        <v>0.46488321116280795</v>
       </c>
       <c r="B17" s="1">
         <v>-4.0121113512360113E-2</v>
@@ -935,10 +935,10 @@
         <v>0.53204081962611061</v>
       </c>
       <c r="E17" s="1">
-        <v>0.44560007112894362</v>
+        <v>-0.44560007112894362</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.54097928529723638</v>
+        <v>0.54097928529723638</v>
       </c>
       <c r="G17" s="1">
         <v>0.2876669963172751</v>
@@ -950,12 +950,12 @@
         <v>-0.2579059373994243</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.56769515122064496</v>
+        <v>0.56769515122064496</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>0.82327335192709694</v>
+        <v>-0.82327335192709694</v>
       </c>
       <c r="B18" s="1">
         <v>-0.92278561078424926</v>
@@ -967,10 +967,10 @@
         <v>0.24490767887551115</v>
       </c>
       <c r="E18" s="1">
-        <v>1.628029007768707</v>
+        <v>-1.628029007768707</v>
       </c>
       <c r="F18" s="1">
-        <v>1.5724335060973607</v>
+        <v>-1.5724335060973607</v>
       </c>
       <c r="G18" s="1">
         <v>1.9451830559700212</v>
@@ -982,12 +982,12 @@
         <v>2.1369740636592089</v>
       </c>
       <c r="J18" s="1">
-        <v>1.9460061695330835</v>
+        <v>-1.9460061695330835</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>1.2062388166294982</v>
+        <v>-1.2062388166294982</v>
       </c>
       <c r="B19" s="1">
         <v>-0.25410038557827275</v>
@@ -999,10 +999,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E19" s="1">
-        <v>0.40306665614190423</v>
+        <v>-0.40306665614190423</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.17773646177628877</v>
+        <v>0.17773646177628877</v>
       </c>
       <c r="G19" s="1">
         <v>1.0564344985154648</v>
@@ -1014,12 +1014,12 @@
         <v>0.21113022363800002</v>
       </c>
       <c r="J19" s="1">
-        <v>0.73070429131743808</v>
+        <v>-0.73070429131743808</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>-0.53451329565415251</v>
+        <v>0.53451329565415251</v>
       </c>
       <c r="B20" s="1">
         <v>-0.14711074954531644</v>
@@ -1031,10 +1031,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.1876830643734639</v>
+        <v>1.1876830643734639</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.24378061150736854</v>
+        <v>0.24378061150736854</v>
       </c>
       <c r="G20" s="1">
         <v>-0.33890073668818715</v>
@@ -1046,12 +1046,12 @@
         <v>-1.1400666641188173</v>
       </c>
       <c r="J20" s="1">
-        <v>-1.0225059273782702</v>
+        <v>1.0225059273782702</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>-1.1611840560762658</v>
+        <v>1.1611840560762658</v>
       </c>
       <c r="B21" s="1">
         <v>-6.6868522520598592E-2</v>
@@ -1063,10 +1063,10 @@
         <v>-1.7650243063786977</v>
       </c>
       <c r="E21" s="1">
-        <v>0.26695972818336722</v>
+        <v>-0.26695972818336722</v>
       </c>
       <c r="F21" s="1">
-        <v>0.44968296066898389</v>
+        <v>-0.44968296066898389</v>
       </c>
       <c r="G21" s="1">
         <v>0.75870373176818939</v>
@@ -1078,12 +1078,12 @@
         <v>0.25461702002557479</v>
       </c>
       <c r="J21" s="1">
-        <v>0.12231140967101865</v>
+        <v>-0.12231140967101865</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>1.0321636054011305</v>
+        <v>-1.0321636054011305</v>
       </c>
       <c r="B22" s="1">
         <v>0.70880633871833421</v>
@@ -1095,10 +1095,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E22" s="1">
-        <v>0.5306669011030285</v>
+        <v>-0.5306669011030285</v>
       </c>
       <c r="F22" s="1">
-        <v>0.8789699339210113</v>
+        <v>-0.8789699339210113</v>
       </c>
       <c r="G22" s="1">
         <v>-0.68551267409546457</v>
@@ -1110,12 +1110,12 @@
         <v>1.2734505353916359</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.72498696940240159</v>
+        <v>0.72498696940240159</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>0.92771847866411383</v>
+        <v>-0.92771847866411383</v>
       </c>
       <c r="B23" s="1">
         <v>-0.20060556756179579</v>
@@ -1127,10 +1127,10 @@
         <v>0.53204081962611061</v>
       </c>
       <c r="E23" s="1">
-        <v>1.0495745639449383</v>
+        <v>-1.0495745639449383</v>
       </c>
       <c r="F23" s="1">
-        <v>0.18550636174465884</v>
+        <v>-0.18550636174465884</v>
       </c>
       <c r="G23" s="1">
         <v>-0.62774401786091893</v>
@@ -1142,12 +1142,12 @@
         <v>0.32295341434890884</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.98392491537142568</v>
+        <v>0.98392491537142568</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>0.54475301396171261</v>
+        <v>-0.54475301396171261</v>
       </c>
       <c r="B24" s="1">
         <v>-4.0121113512360113E-2</v>
@@ -1159,10 +1159,10 @@
         <v>0.24490767887551115</v>
       </c>
       <c r="E24" s="1">
-        <v>0.74333397603823759</v>
+        <v>-0.74333397603823759</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.22726957407459861</v>
+        <v>0.22726957407459861</v>
       </c>
       <c r="G24" s="1">
         <v>0.98533461391910193</v>
@@ -1174,12 +1174,12 @@
         <v>-0.49087091804715133</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.26053094024306517</v>
+        <v>0.26053094024306517</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>0.26623267599632827</v>
+        <v>-0.26623267599632827</v>
       </c>
       <c r="B25" s="1">
         <v>-0.33434261260299059</v>
@@ -1191,10 +1191,10 @@
         <v>1.6805733826285167</v>
       </c>
       <c r="E25" s="1">
-        <v>0.52216021810561575</v>
+        <v>-0.52216021810561575</v>
       </c>
       <c r="F25" s="1">
-        <v>0.44968296066898389</v>
+        <v>-0.44968296066898389</v>
       </c>
       <c r="G25" s="1">
         <v>-0.70773138803182878</v>
@@ -1206,12 +1206,12 @@
         <v>-0.69898630075912027</v>
       </c>
       <c r="J25" s="1">
-        <v>0.12231140967101865</v>
+        <v>-0.12231140967101865</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>-0.77821859137386462</v>
+        <v>0.77821859137386462</v>
       </c>
       <c r="B26" s="1">
         <v>0.36109002161122672</v>
@@ -1223,10 +1223,10 @@
         <v>0.53204081962611061</v>
       </c>
       <c r="E26" s="1">
-        <v>0.3094931431704066</v>
+        <v>-0.3094931431704066</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.24378061150736854</v>
+        <v>0.24378061150736854</v>
       </c>
       <c r="G26" s="1">
         <v>-0.85437490001182981</v>
@@ -1238,12 +1238,12 @@
         <v>-0.93505748114881748</v>
       </c>
       <c r="J26" s="1">
-        <v>0.69583299200355608</v>
+        <v>-0.69583299200355608</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>0.37067780273334511</v>
+        <v>-0.37067780273334511</v>
       </c>
       <c r="B27" s="1">
         <v>-0.70880633871833654</v>
@@ -1255,10 +1255,10 @@
         <v>0.81917396037671419</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.84741574447713053</v>
+        <v>0.84741574447713053</v>
       </c>
       <c r="F27" s="1">
-        <v>0.46619399810175383</v>
+        <v>-0.46619399810175383</v>
       </c>
       <c r="G27" s="1">
         <v>-0.97435595526819474</v>
@@ -1270,12 +1270,12 @@
         <v>-0.531251514692757</v>
       </c>
       <c r="J27" s="1">
-        <v>-0.45417794281588886</v>
+        <v>0.45417794281588886</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>-0.43006816891713567</v>
+        <v>0.43006816891713567</v>
       </c>
       <c r="B28" s="1">
         <v>-0.30759520359474973</v>
@@ -1287,10 +1287,10 @@
         <v>-1.477891165628096</v>
       </c>
       <c r="E28" s="1">
-        <v>-0.62624198654450869</v>
+        <v>0.62624198654450869</v>
       </c>
       <c r="F28" s="1">
-        <v>3.6907024849726397E-2</v>
+        <v>-3.6907024849726397E-2</v>
       </c>
       <c r="G28" s="1">
         <v>-0.85881864279910336</v>
@@ -1302,12 +1302,12 @@
         <v>-1.4475804385738165</v>
       </c>
       <c r="J28" s="1">
-        <v>-1.0603449968465264</v>
+        <v>1.0603449968465264</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>0.99734856315545828</v>
+        <v>-0.99734856315545828</v>
       </c>
       <c r="B29" s="1">
         <v>-0.22735297657003428</v>
@@ -1319,10 +1319,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E29" s="1">
-        <v>1.5259488117998026</v>
+        <v>-1.5259488117998026</v>
       </c>
       <c r="F29" s="1">
-        <v>0.11946221201357614</v>
+        <v>-0.11946221201357614</v>
       </c>
       <c r="G29" s="1">
         <v>0.87424104423728233</v>
@@ -1334,12 +1334,12 @@
         <v>-0.39768492578806031</v>
       </c>
       <c r="J29" s="1">
-        <v>2.0016518599275726</v>
+        <v>-2.0016518599275726</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>0.12697250701363302</v>
+        <v>-0.12697250701363302</v>
       </c>
       <c r="B30" s="1">
         <v>-0.5215744756606624</v>
@@ -1351,10 +1351,10 @@
         <v>-0.90362488412689501</v>
       </c>
       <c r="E30" s="1">
-        <v>-0.95800262344343545</v>
+        <v>0.95800262344343545</v>
       </c>
       <c r="F30" s="1">
-        <v>0.82943682162269849</v>
+        <v>-0.82943682162269849</v>
       </c>
       <c r="G30" s="1">
         <v>-0.86326238558637525</v>
@@ -1366,12 +1366,12 @@
         <v>-0.95680087934260538</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.30653137763584332</v>
+        <v>0.30653137763584332</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>0.96253352090978606</v>
+        <v>-0.96253352090978606</v>
       </c>
       <c r="B31" s="1">
         <v>-1.337370450412162E-2</v>
@@ -1383,10 +1383,10 @@
         <v>-1.477891165628096</v>
       </c>
       <c r="E31" s="1">
-        <v>-8.1814274710372864E-2</v>
+        <v>8.1814274710372864E-2</v>
       </c>
       <c r="F31" s="1">
-        <v>0.74688163445884881</v>
+        <v>-0.74688163445884881</v>
       </c>
       <c r="G31" s="1">
         <v>9.2142313677272145E-2</v>
@@ -1398,12 +1398,12 @@
         <v>-0.82944668992184789</v>
       </c>
       <c r="J31" s="1">
-        <v>1.3101614139587199</v>
+        <v>-1.3101614139587199</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>0.71882822519007394</v>
+        <v>-0.71882822519007394</v>
       </c>
       <c r="B32" s="1">
         <v>-2.34039828822092</v>
@@ -1415,10 +1415,10 @@
         <v>-0.61649174337629353</v>
       </c>
       <c r="E32" s="1">
-        <v>1.6025089587764809</v>
+        <v>-1.6025089587764809</v>
       </c>
       <c r="F32" s="1">
-        <v>1.2752348323074987</v>
+        <v>-1.2752348323074987</v>
       </c>
       <c r="G32" s="1">
         <v>0.94978467162091884</v>
@@ -1430,12 +1430,12 @@
         <v>-0.15540134591442381</v>
       </c>
       <c r="J32" s="1">
-        <v>1.3947428633583425</v>
+        <v>-1.3947428633583425</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>0.85808839417276928</v>
+        <v>-0.85808839417276928</v>
       </c>
       <c r="B33" s="1">
         <v>-1.7787026990478998</v>
@@ -1447,10 +1447,10 @@
         <v>-0.32935860262569194</v>
       </c>
       <c r="E33" s="1">
-        <v>0.79437407402268367</v>
+        <v>-0.79437407402268367</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.17773646177628877</v>
+        <v>0.17773646177628877</v>
       </c>
       <c r="G33" s="1">
         <v>-0.70773138803182878</v>
@@ -1462,12 +1462,12 @@
         <v>-0.24548113843154576</v>
       </c>
       <c r="J33" s="1">
-        <v>1.3005161609570086</v>
+        <v>-1.3005161609570086</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>1.2062388166294982</v>
+        <v>-1.2062388166294982</v>
       </c>
       <c r="B34" s="1">
         <v>0.25410038557827042</v>
@@ -1479,10 +1479,10 @@
         <v>-0.61649174337629353</v>
       </c>
       <c r="E34" s="1">
-        <v>1.1431480769164297</v>
+        <v>-1.1431480769164297</v>
       </c>
       <c r="F34" s="1">
-        <v>1.8035880301561458</v>
+        <v>-1.8035880301561458</v>
       </c>
       <c r="G34" s="1">
         <v>-1.6764673156572951</v>
@@ -1494,12 +1494,12 @@
         <v>-0.6058003085000303</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.46085542566322568</v>
+        <v>0.46085542566322568</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>3.1210661401415103</v>
+        <v>-3.1210661401415103</v>
       </c>
       <c r="B35" s="1">
         <v>-3.3835472395422426</v>
@@ -1511,10 +1511,10 @@
         <v>-2.6264237286305021</v>
       </c>
       <c r="E35" s="1">
-        <v>2.5127240394991763</v>
+        <v>-2.5127240394991763</v>
       </c>
       <c r="F35" s="1">
-        <v>3.2070262119416237</v>
+        <v>-3.2070262119416237</v>
       </c>
       <c r="G35" s="1">
         <v>-3.2895459474373143</v>
@@ -1526,7 +1526,7 @@
         <v>-3.0659105041400272</v>
       </c>
       <c r="J35" s="1">
-        <v>0.37457187279270587</v>
+        <v>-0.37457187279270587</v>
       </c>
     </row>
   </sheetData>
